--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G17">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,55 +635,55 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -638,10 +638,10 @@
         <v>2.45</v>
       </c>
       <c r="O2">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -650,7 +650,7 @@
         <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="T2">
         <v>1.9</v>
@@ -662,37 +662,37 @@
         <v>1.14</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AA2">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AB2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1133,19 +1133,19 @@
         <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="S5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
         <v>1.7</v>
@@ -1157,10 +1157,10 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
         <v>1.37</v>
@@ -1172,16 +1172,16 @@
         <v>2.02</v>
       </c>
       <c r="AD5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF5">
         <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>1.18</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O9">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
         <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
+        <v>1.87</v>
+      </c>
+      <c r="AG9">
         <v>1.85</v>
       </c>
-      <c r="AG9">
-        <v>1.91</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>1.4</v>
       </c>
       <c r="O12">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="V12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
         <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC12">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE12">
         <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.06</v>
       </c>
       <c r="AK12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O2">
         <v>2.45</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -650,13 +650,13 @@
         <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V2">
         <v>1.14</v>
@@ -665,19 +665,19 @@
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Y2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AA2">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AB2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
         <v>6.5</v>
@@ -689,7 +689,7 @@
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG2">
         <v>1.5</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
         <v>2.68</v>
       </c>
       <c r="P6">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="R6">
         <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="U6">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V6">
         <v>1.21</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AA6">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AB6">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC6">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="AD6">
         <v>1.12</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
         <v>2.15</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.5</v>
       </c>
       <c r="AK6">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1779,25 +1779,25 @@
         <v>2.05</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
         <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R9">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U9">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="V9">
         <v>1.33</v>
@@ -1806,28 +1806,28 @@
         <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
         <v>2.12</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
         <v>1.87</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,61 +2265,61 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Q12">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U12">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
         <v>1.64</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="AA12">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE12">
         <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
         <v>2.04</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1133,25 +1133,25 @@
         <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="R5">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V5">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,10 +1160,10 @@
         <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB5">
         <v>2.66</v>
@@ -1178,10 +1178,10 @@
         <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG5">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
         <v>1.18</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1782,7 +1782,7 @@
         <v>3.2</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="Q9">
         <v>2.46</v>
@@ -1797,7 +1797,7 @@
         <v>2.47</v>
       </c>
       <c r="U9">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="V9">
         <v>1.33</v>
@@ -1812,10 +1812,10 @@
         <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AA9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB9">
         <v>1.74</v>
@@ -1833,7 +1833,7 @@
         <v>1.87</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="O12">
         <v>5.25</v>
       </c>
       <c r="P12">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
         <v>2.46</v>
@@ -2286,13 +2286,13 @@
         <v>3.94</v>
       </c>
       <c r="U12">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2301,25 +2301,25 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AD12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG12">
         <v>2.04</v>
@@ -2338,7 +2338,7 @@
         <v>1.11</v>
       </c>
       <c r="AK12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="P2">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
         <v>1.79</v>
@@ -659,37 +659,37 @@
         <v>4.8</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1.17</v>
       </c>
       <c r="Y2">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z2">
         <v>2.08</v>
       </c>
       <c r="AA2">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AB2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD2">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG2">
         <v>1.5</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
+        <v>3.1</v>
+      </c>
+      <c r="O5">
         <v>3.7</v>
       </c>
-      <c r="O5">
-        <v>3.95</v>
-      </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>4.24</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="U5">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AD5">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE5">
+        <v>1.24</v>
+      </c>
+      <c r="AF5">
+        <v>1.4</v>
+      </c>
+      <c r="AG5">
+        <v>2.62</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.2</v>
+      </c>
+      <c r="AK5">
         <v>1.26</v>
-      </c>
-      <c r="AF5">
-        <v>1.38</v>
-      </c>
-      <c r="AG5">
-        <v>2.75</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.18</v>
-      </c>
-      <c r="AK5">
-        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,49 +1450,49 @@
         </is>
       </c>
       <c r="N7">
+        <v>3.2</v>
+      </c>
+      <c r="O7">
+        <v>2.75</v>
+      </c>
+      <c r="P7">
+        <v>2.25</v>
+      </c>
+      <c r="Q7">
+        <v>3.75</v>
+      </c>
+      <c r="R7">
+        <v>1.85</v>
+      </c>
+      <c r="S7">
+        <v>1.62</v>
+      </c>
+      <c r="T7">
+        <v>2.15</v>
+      </c>
+      <c r="U7">
         <v>3.5</v>
       </c>
-      <c r="O7">
-        <v>2.68</v>
-      </c>
-      <c r="P7">
-        <v>2.3</v>
-      </c>
-      <c r="Q7">
-        <v>4.31</v>
-      </c>
-      <c r="R7">
-        <v>1.91</v>
-      </c>
-      <c r="S7">
-        <v>1.63</v>
-      </c>
-      <c r="T7">
-        <v>2.13</v>
-      </c>
-      <c r="U7">
-        <v>3.58</v>
-      </c>
       <c r="V7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1.08</v>
       </c>
       <c r="Y7">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z7">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AA7">
         <v>2.49</v>
       </c>
       <c r="AB7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC7">
         <v>5.25</v>
@@ -1501,10 +1501,10 @@
         <v>1.12</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG7">
         <v>1.58</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
         <v>1.27</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>3.2</v>
       </c>
       <c r="P9">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
         <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U9">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1812,13 +1812,13 @@
         <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.8</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,28 +2268,28 @@
         <v>1.31</v>
       </c>
       <c r="O12">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P12">
-        <v>8.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q12">
         <v>1.75</v>
       </c>
       <c r="R12">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="S12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="U12">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W12">
         <v>1.17</v>
@@ -2301,28 +2301,28 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB12">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC12">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE12">
         <v>1.26</v>
       </c>
       <c r="AF12">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK12">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G15">
@@ -2857,984 +2857,6 @@
         <v>0</v>
       </c>
       <c r="AU15" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Qabala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>İnter Bakı</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>-1</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Kapaz</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Turan</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-1</v>
-      </c>
-      <c r="AN17">
-        <v>-1</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>-1</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Safa</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Mil Mugan FK</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Araz</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sabah</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Zira</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Neftçi</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2026-08-27 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
         <is>
           <t>2026-08-27 21:30:00</t>
         </is>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -638,16 +638,16 @@
         <v>2.3</v>
       </c>
       <c r="O2">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="S2">
         <v>1.79</v>
@@ -656,28 +656,28 @@
         <v>1.91</v>
       </c>
       <c r="U2">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="V2">
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y2">
         <v>1.73</v>
       </c>
       <c r="Z2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AA2">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="AB2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
         <v>6.2</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R5">
         <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T5">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U5">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="V5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,28 +1160,28 @@
         <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC5">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE5">
         <v>1.24</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG5">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,25 +1456,25 @@
         <v>2.75</v>
       </c>
       <c r="P7">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q7">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T7">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="U7">
         <v>3.5</v>
       </c>
       <c r="V7">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
         <v>1.02</v>
@@ -1483,31 +1483,31 @@
         <v>1.08</v>
       </c>
       <c r="Y7">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Z7">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AA7">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AB7">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC7">
         <v>5.25</v>
       </c>
       <c r="AD7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
         <v>2.14</v>
       </c>
       <c r="AG7">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
         <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R9">
         <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U9">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1809,19 +1809,19 @@
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA9">
         <v>2.13</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
@@ -1830,10 +1830,10 @@
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,22 +2111,22 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="R11">
         <v>2.62</v>
       </c>
       <c r="S11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="V11">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="W11">
         <v>1.29</v>
@@ -2144,7 +2144,7 @@
         <v>1.3</v>
       </c>
       <c r="AB11">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AC11">
         <v>1.77</v>
@@ -2153,13 +2153,13 @@
         <v>1.86</v>
       </c>
       <c r="AE11">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK11">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O12">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="P12">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R12">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="S12">
         <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA12">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB12">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AC12">
         <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -2114,7 +2114,7 @@
         <v>1.53</v>
       </c>
       <c r="R11">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S11">
         <v>1.14</v>
@@ -2123,10 +2123,10 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W11">
         <v>1.29</v>
@@ -2138,7 +2138,7 @@
         <v>1.06</v>
       </c>
       <c r="Z11">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA11">
         <v>1.3</v>
@@ -2156,10 +2156,10 @@
         <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
         <v>1.53</v>
       </c>
       <c r="R11">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="S11">
         <v>1.14</v>
@@ -2129,16 +2129,16 @@
         <v>1.77</v>
       </c>
       <c r="W11">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z11">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>1.3</v>
@@ -2147,19 +2147,19 @@
         <v>3.4</v>
       </c>
       <c r="AC11">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD11">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AE11">
         <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -638,16 +638,16 @@
         <v>2.3</v>
       </c>
       <c r="O2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q2">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="R2">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
         <v>1.79</v>
@@ -671,25 +671,25 @@
         <v>1.73</v>
       </c>
       <c r="Z2">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AA2">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AB2">
         <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>6.2</v>
+        <v>6.73</v>
       </c>
       <c r="AD2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG2">
         <v>1.5</v>
@@ -708,7 +708,7 @@
         <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U5">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AA5">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB5">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AC5">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="AD5">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AE5">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="AK5">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.27</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="T6">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="AA6">
-        <v>1.96</v>
+        <v>2.59</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AC6">
-        <v>3.15</v>
+        <v>5.05</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="AG6">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>2.29</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="R7">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.17</v>
+        <v>2.93</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.28</v>
+      </c>
+      <c r="Z7">
+        <v>3.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.85</v>
+      </c>
+      <c r="AB7">
+        <v>1.8</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
         <v>1.08</v>
       </c>
-      <c r="Y7">
-        <v>1.54</v>
-      </c>
-      <c r="Z7">
-        <v>2.28</v>
-      </c>
-      <c r="AA7">
-        <v>2.59</v>
-      </c>
-      <c r="AB7">
-        <v>1.39</v>
-      </c>
-      <c r="AC7">
-        <v>5.25</v>
-      </c>
-      <c r="AD7">
-        <v>1.14</v>
-      </c>
-      <c r="AE7">
-        <v>1.04</v>
-      </c>
       <c r="AF7">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AG7">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.23</v>
+        <v>3.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,65 +1287,65 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.93</v>
       </c>
       <c r="U6">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
+        <v>1.28</v>
+      </c>
+      <c r="Z6">
+        <v>3.4</v>
+      </c>
+      <c r="AA6">
+        <v>1.85</v>
+      </c>
+      <c r="AB6">
+        <v>1.8</v>
+      </c>
+      <c r="AC6">
+        <v>3.14</v>
+      </c>
+      <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
+        <v>1.08</v>
+      </c>
+      <c r="AF6">
+        <v>2.45</v>
+      </c>
+      <c r="AG6">
         <v>1.53</v>
       </c>
-      <c r="Z6">
-        <v>2.34</v>
-      </c>
-      <c r="AA6">
-        <v>2.59</v>
-      </c>
-      <c r="AB6">
-        <v>1.47</v>
-      </c>
-      <c r="AC6">
-        <v>5.05</v>
-      </c>
-      <c r="AD6">
-        <v>1.1</v>
-      </c>
-      <c r="AE6">
-        <v>1.01</v>
-      </c>
-      <c r="AF6">
-        <v>2.14</v>
-      </c>
-      <c r="AG6">
-        <v>1.65</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>3.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="T7">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="U7">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>5.05</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1794,10 +1794,10 @@
         <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V9">
         <v>1.35</v>
@@ -1809,16 +1809,16 @@
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AA9">
         <v>2.13</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.84</v>
@@ -1827,13 +1827,13 @@
         <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O11">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P11">
         <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R11">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S11">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U11">
         <v>1.93</v>
@@ -2135,10 +2135,10 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="AA11">
         <v>1.3</v>
@@ -2147,10 +2147,10 @@
         <v>3.4</v>
       </c>
       <c r="AC11">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD11">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE11">
         <v>1.36</v>
@@ -2159,7 +2159,7 @@
         <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O12">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="P12">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
         <v>2.88</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U12">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W12">
         <v>1.15</v>
@@ -2301,28 +2301,28 @@
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
         <v>2.85</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE12">
         <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK12">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,19 +2630,19 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>3.65</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="T6">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC6">
-        <v>3.14</v>
+        <v>5.05</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="R7">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.28</v>
+        <v>2.93</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
+        <v>1.28</v>
+      </c>
+      <c r="Z7">
+        <v>3.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.85</v>
+      </c>
+      <c r="AB7">
+        <v>1.8</v>
+      </c>
+      <c r="AC7">
+        <v>3.14</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>2.45</v>
+      </c>
+      <c r="AG7">
         <v>1.53</v>
       </c>
-      <c r="Z7">
-        <v>2.34</v>
-      </c>
-      <c r="AA7">
-        <v>2.59</v>
-      </c>
-      <c r="AB7">
-        <v>1.47</v>
-      </c>
-      <c r="AC7">
-        <v>5.05</v>
-      </c>
-      <c r="AD7">
-        <v>1.1</v>
-      </c>
-      <c r="AE7">
-        <v>1.01</v>
-      </c>
-      <c r="AF7">
-        <v>2.14</v>
-      </c>
-      <c r="AG7">
-        <v>1.65</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.22</v>
+        <v>3.3</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,55 +635,55 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="P2">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="Q2">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
         <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="U2">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1.13</v>
       </c>
       <c r="Y2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z2">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AA2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC2">
-        <v>6.73</v>
+        <v>6.85</v>
       </c>
       <c r="AD2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="O5">
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q5">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
         <v>2.21</v>
@@ -1142,16 +1142,16 @@
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,7 +1160,7 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
         <v>1.49</v>
@@ -1169,16 +1169,16 @@
         <v>2.55</v>
       </c>
       <c r="AC5">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG5">
         <v>2.63</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -1302,46 +1302,46 @@
         <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AA6">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AB6">
         <v>1.47</v>
       </c>
       <c r="AC6">
-        <v>5.05</v>
+        <v>5.56</v>
       </c>
       <c r="AD6">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE6">
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG6">
         <v>1.65</v>
@@ -1360,7 +1360,7 @@
         <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>1.26</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q7">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>1.38</v>
@@ -1471,40 +1471,40 @@
         <v>2.93</v>
       </c>
       <c r="U7">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
         <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AG7">
         <v>1.53</v>
@@ -1523,7 +1523,7 @@
         <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="Q8">
         <v>2.38</v>
       </c>
       <c r="R8">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
         <v>1.5</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U8">
         <v>3.32</v>
@@ -1646,25 +1646,25 @@
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AA8">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB8">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC8">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
         <v>2.12</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,55 +1779,55 @@
         <v>1.95</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P9">
         <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
         <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V9">
         <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
         <v>2.93</v>
       </c>
       <c r="AA9">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
         <v>3.84</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P11">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q11">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="S11">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="T11">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="U11">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="V11">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="W11">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z11">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA11">
+        <v>1.4</v>
+      </c>
+      <c r="AB11">
+        <v>2.88</v>
+      </c>
+      <c r="AC11">
+        <v>2.07</v>
+      </c>
+      <c r="AD11">
+        <v>1.86</v>
+      </c>
+      <c r="AE11">
         <v>1.3</v>
       </c>
-      <c r="AB11">
-        <v>3.4</v>
-      </c>
-      <c r="AC11">
-        <v>1.77</v>
-      </c>
-      <c r="AD11">
-        <v>1.92</v>
-      </c>
-      <c r="AE11">
-        <v>1.36</v>
-      </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,49 +2265,49 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O12">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="P12">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA12">
         <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC12">
         <v>2.2</v>
@@ -2316,13 +2316,13 @@
         <v>1.68</v>
       </c>
       <c r="AE12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
         <v>1.72</v>
       </c>
       <c r="AG12">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O13">
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T13">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W13">
         <v>1.04</v>
       </c>
       <c r="X13">
+        <v>1.07</v>
+      </c>
+      <c r="Y13">
+        <v>1.44</v>
+      </c>
+      <c r="Z13">
+        <v>2.7</v>
+      </c>
+      <c r="AA13">
+        <v>2.45</v>
+      </c>
+      <c r="AB13">
+        <v>1.57</v>
+      </c>
+      <c r="AC13">
+        <v>4.5</v>
+      </c>
+      <c r="AD13">
+        <v>1.16</v>
+      </c>
+      <c r="AE13">
         <v>1.05</v>
       </c>
-      <c r="Y13">
-        <v>1.41</v>
-      </c>
-      <c r="Z13">
-        <v>2.52</v>
-      </c>
-      <c r="AA13">
-        <v>2.35</v>
-      </c>
-      <c r="AB13">
-        <v>1.53</v>
-      </c>
-      <c r="AC13">
-        <v>4.25</v>
-      </c>
-      <c r="AD13">
-        <v>1.15</v>
-      </c>
-      <c r="AE13">
-        <v>1.01</v>
-      </c>
       <c r="AF13">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG13">
         <v>1.5</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK13">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB14">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="P2">
         <v>3.73</v>
@@ -656,10 +656,10 @@
         <v>2.15</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -677,10 +677,10 @@
         <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AD2">
         <v>1.06</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.56</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="P6">
-        <v>2.15</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="V6">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AC6">
-        <v>5.56</v>
+        <v>3.45</v>
       </c>
       <c r="AD6">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>1.29</v>
+        <v>3.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>9.779999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="T7">
-        <v>2.93</v>
+        <v>2.11</v>
       </c>
       <c r="U7">
-        <v>2.78</v>
+        <v>3.72</v>
       </c>
       <c r="V7">
+        <v>1.2</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1.08</v>
+      </c>
+      <c r="Y7">
+        <v>1.55</v>
+      </c>
+      <c r="Z7">
+        <v>2.28</v>
+      </c>
+      <c r="AA7">
+        <v>2.63</v>
+      </c>
+      <c r="AB7">
+        <v>1.47</v>
+      </c>
+      <c r="AC7">
+        <v>5.63</v>
+      </c>
+      <c r="AD7">
+        <v>1.14</v>
+      </c>
+      <c r="AE7">
+        <v>1.01</v>
+      </c>
+      <c r="AF7">
+        <v>2.15</v>
+      </c>
+      <c r="AG7">
+        <v>1.65</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.36</v>
       </c>
-      <c r="W7">
-        <v>1.05</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.3</v>
-      </c>
-      <c r="Z7">
-        <v>3.08</v>
-      </c>
-      <c r="AA7">
-        <v>1.92</v>
-      </c>
-      <c r="AB7">
-        <v>1.79</v>
-      </c>
-      <c r="AC7">
-        <v>3.42</v>
-      </c>
-      <c r="AD7">
-        <v>1.27</v>
-      </c>
-      <c r="AE7">
-        <v>1.07</v>
-      </c>
-      <c r="AF7">
-        <v>2.57</v>
-      </c>
-      <c r="AG7">
-        <v>1.53</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.12</v>
-      </c>
       <c r="AK7">
-        <v>3.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O9">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
         <v>3.75</v>
@@ -1794,10 +1794,10 @@
         <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U9">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="V9">
         <v>1.35</v>
@@ -1809,7 +1809,7 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
         <v>2.93</v>
@@ -1818,7 +1818,7 @@
         <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC9">
         <v>3.84</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O12">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R12">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="V12">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2301,25 +2301,25 @@
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF12">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG12">
         <v>2.1</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
         <v>3.4</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>9.779999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>2.11</v>
       </c>
       <c r="U6">
-        <v>2.78</v>
+        <v>3.72</v>
       </c>
       <c r="V6">
+        <v>1.2</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1.08</v>
+      </c>
+      <c r="Y6">
+        <v>1.55</v>
+      </c>
+      <c r="Z6">
+        <v>2.28</v>
+      </c>
+      <c r="AA6">
+        <v>2.63</v>
+      </c>
+      <c r="AB6">
+        <v>1.47</v>
+      </c>
+      <c r="AC6">
+        <v>5.63</v>
+      </c>
+      <c r="AD6">
+        <v>1.14</v>
+      </c>
+      <c r="AE6">
+        <v>1.01</v>
+      </c>
+      <c r="AF6">
+        <v>2.15</v>
+      </c>
+      <c r="AG6">
+        <v>1.65</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.36</v>
       </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.33</v>
-      </c>
-      <c r="Z6">
-        <v>3.08</v>
-      </c>
-      <c r="AA6">
-        <v>1.92</v>
-      </c>
-      <c r="AB6">
-        <v>1.79</v>
-      </c>
-      <c r="AC6">
-        <v>3.45</v>
-      </c>
-      <c r="AD6">
-        <v>1.27</v>
-      </c>
-      <c r="AE6">
-        <v>1.07</v>
-      </c>
-      <c r="AF6">
-        <v>2.65</v>
-      </c>
-      <c r="AG6">
-        <v>1.37</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.12</v>
-      </c>
       <c r="AK6">
-        <v>3.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>1.78</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.11</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>3.72</v>
+        <v>2.78</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="AB7">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>5.63</v>
+        <v>3.45</v>
       </c>
       <c r="AD7">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.29</v>
+        <v>3.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T11">
         <v>3.9</v>
       </c>
       <c r="U11">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V11">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W11">
         <v>1.17</v>
@@ -2138,28 +2138,28 @@
         <v>1.09</v>
       </c>
       <c r="Z11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA11">
         <v>1.4</v>
       </c>
       <c r="AB11">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AC11">
         <v>2.07</v>
       </c>
       <c r="AD11">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="O14">
         <v>3.55</v>
       </c>
       <c r="P14">
-        <v>3.09</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.24</v>
@@ -2612,10 +2612,10 @@
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
         <v>1.15</v>
@@ -2630,16 +2630,16 @@
         <v>5.5</v>
       </c>
       <c r="AA14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AC14">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD14">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE14">
         <v>1.18</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O15">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="P15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q15">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="R15">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="S15">
         <v>1.11</v>
       </c>
       <c r="T15">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V15">
         <v>2.2</v>
       </c>
       <c r="W15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -2796,22 +2796,22 @@
         <v>1.18</v>
       </c>
       <c r="AB15">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AC15">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AD15">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AE15">
         <v>1.59</v>
       </c>
       <c r="AF15">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK15">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -2105,10 +2105,10 @@
         <v>1.27</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="P11">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -2120,7 +2120,7 @@
         <v>1.2</v>
       </c>
       <c r="T11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U11">
         <v>2.07</v>
@@ -2138,19 +2138,19 @@
         <v>1.09</v>
       </c>
       <c r="Z11">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AC11">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE11">
         <v>1.27</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="S14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="V14">
         <v>1.62</v>
@@ -2624,16 +2624,16 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z14">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB14">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="AC14">
         <v>2.27</v>
@@ -2642,10 +2642,10 @@
         <v>1.56</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG14">
         <v>2.63</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,49 +2754,49 @@
         </is>
       </c>
       <c r="N15">
+        <v>1.08</v>
+      </c>
+      <c r="O15">
+        <v>10.5</v>
+      </c>
+      <c r="P15">
+        <v>16.5</v>
+      </c>
+      <c r="Q15">
+        <v>1.28</v>
+      </c>
+      <c r="R15">
+        <v>3.15</v>
+      </c>
+      <c r="S15">
         <v>1.1</v>
-      </c>
-      <c r="O15">
-        <v>9.25</v>
-      </c>
-      <c r="P15">
-        <v>14</v>
-      </c>
-      <c r="Q15">
-        <v>1.4</v>
-      </c>
-      <c r="R15">
-        <v>3.25</v>
-      </c>
-      <c r="S15">
-        <v>1.11</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="V15">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="W15">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z15">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB15">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="AC15">
         <v>1.38</v>
@@ -2805,13 +2805,13 @@
         <v>2.63</v>
       </c>
       <c r="AE15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF15">
         <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK15">
-        <v>5.65</v>
+        <v>9</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O2">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="P2">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="T2">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -677,16 +677,16 @@
         <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="AD2">
         <v>1.06</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
         <v>2.4</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
@@ -1148,7 +1148,7 @@
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
         <v>1.13</v>
@@ -1160,28 +1160,28 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA5">
         <v>1.49</v>
       </c>
       <c r="AB5">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD5">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE5">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
         <v>1.46</v>
       </c>
       <c r="AG5">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R6">
         <v>1.93</v>
       </c>
       <c r="S6">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T6">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U6">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V6">
         <v>1.2</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y6">
         <v>1.55</v>
       </c>
       <c r="Z6">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AA6">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB6">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC6">
-        <v>5.63</v>
+        <v>5.25</v>
       </c>
       <c r="AD6">
         <v>1.14</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
         <v>2.15</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AK6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,25 +1456,25 @@
         <v>4.3</v>
       </c>
       <c r="P7">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="Q7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
         <v>1.05</v>
@@ -1483,25 +1483,25 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
         <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
         <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
         <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>2.65</v>
@@ -1523,7 +1523,7 @@
         <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O8">
         <v>3.2</v>
       </c>
       <c r="P8">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
         <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
         <v>3.32</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA8">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC8">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD8">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK8">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
         <v>1.47</v>
       </c>
       <c r="T9">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U9">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1812,28 +1812,28 @@
         <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AA9">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB9">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="AD9">
         <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
         <v>1.88</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
+        <v>3.2</v>
+      </c>
+      <c r="P10">
+        <v>2.92</v>
+      </c>
+      <c r="Q10">
+        <v>2.75</v>
+      </c>
+      <c r="R10">
+        <v>2.1</v>
+      </c>
+      <c r="S10">
+        <v>1.36</v>
+      </c>
+      <c r="T10">
+        <v>2.88</v>
+      </c>
+      <c r="U10">
+        <v>2.75</v>
+      </c>
+      <c r="V10">
+        <v>1.36</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1.3</v>
+      </c>
+      <c r="Z10">
         <v>3</v>
       </c>
-      <c r="P10">
-        <v>2.62</v>
-      </c>
-      <c r="Q10">
-        <v>2.94</v>
-      </c>
-      <c r="R10">
-        <v>1.98</v>
-      </c>
-      <c r="S10">
-        <v>1.37</v>
-      </c>
-      <c r="T10">
-        <v>2.96</v>
-      </c>
-      <c r="U10">
-        <v>2.82</v>
-      </c>
-      <c r="V10">
-        <v>1.35</v>
-      </c>
-      <c r="W10">
+      <c r="AA10">
+        <v>1.87</v>
+      </c>
+      <c r="AB10">
+        <v>1.83</v>
+      </c>
+      <c r="AC10">
+        <v>3.35</v>
+      </c>
+      <c r="AD10">
+        <v>1.27</v>
+      </c>
+      <c r="AE10">
         <v>1.06</v>
       </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>3.41</v>
-      </c>
-      <c r="AA10">
-        <v>2</v>
-      </c>
-      <c r="AB10">
-        <v>1.76</v>
-      </c>
-      <c r="AC10">
-        <v>3.29</v>
-      </c>
-      <c r="AD10">
-        <v>1.31</v>
-      </c>
-      <c r="AE10">
-        <v>1.05</v>
-      </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>7.28</v>
+        <v>7.5</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -2129,7 +2129,7 @@
         <v>1.67</v>
       </c>
       <c r="W11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R12">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U12">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="V12">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB12">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD12">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE12">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
         <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="R13">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="U13">
         <v>3.25</v>
@@ -2455,37 +2455,37 @@
         <v>1.27</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB13">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG13">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK13">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P14">
         <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R14">
         <v>2.27</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="O15">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P15">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Q15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="R15">
         <v>3.15</v>
       </c>
       <c r="S15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -2793,10 +2793,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AB15">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="AC15">
         <v>1.38</v>
@@ -2808,10 +2808,10 @@
         <v>1.6</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.01</v>
       </c>
       <c r="AK15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="O2">
         <v>2.62</v>
@@ -650,16 +650,16 @@
         <v>1.8</v>
       </c>
       <c r="S2">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="T2">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="U2">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -677,22 +677,22 @@
         <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="AD2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>2.75</v>
       </c>
       <c r="P6">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q6">
         <v>4.2</v>
@@ -1338,7 +1338,7 @@
         <v>1.14</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
         <v>2.15</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O7">
         <v>4.3</v>
       </c>
       <c r="P7">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q7">
         <v>1.79</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S7">
         <v>1.36</v>
@@ -1471,10 +1471,10 @@
         <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
         <v>1.05</v>
@@ -1483,25 +1483,25 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
         <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
         <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
         <v>2.65</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="O6">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="P6">
-        <v>2.19</v>
+        <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="R6">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="S6">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AC6">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="P7">
-        <v>9.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="R7">
-        <v>2.56</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U7">
+        <v>3.8</v>
+      </c>
+      <c r="V7">
+        <v>1.2</v>
+      </c>
+      <c r="W7">
+        <v>1.04</v>
+      </c>
+      <c r="X7">
+        <v>1.11</v>
+      </c>
+      <c r="Y7">
+        <v>1.55</v>
+      </c>
+      <c r="Z7">
+        <v>2.35</v>
+      </c>
+      <c r="AA7">
         <v>2.7</v>
       </c>
-      <c r="V7">
-        <v>1.38</v>
-      </c>
-      <c r="W7">
-        <v>1.05</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.28</v>
-      </c>
-      <c r="Z7">
-        <v>3.4</v>
-      </c>
-      <c r="AA7">
-        <v>1.9</v>
-      </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="AK7">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,42 +624,42 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R2">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="S2">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="T2">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -680,23 +680,23 @@
         <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AD2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG2">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "86"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA4">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "90+1", "90+8"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="O5">
         <v>3.5</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
       </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
         <v>2.2</v>
@@ -1157,28 +1157,28 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
         <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC5">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD5">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG5">
         <v>2.45</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AK5">
         <v>1.29</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>9.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q6">
-        <v>1.79</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S6">
+        <v>1.63</v>
+      </c>
+      <c r="T6">
+        <v>2.13</v>
+      </c>
+      <c r="U6">
+        <v>3.9</v>
+      </c>
+      <c r="V6">
+        <v>1.2</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1.11</v>
+      </c>
+      <c r="Y6">
+        <v>1.55</v>
+      </c>
+      <c r="Z6">
+        <v>2.35</v>
+      </c>
+      <c r="AA6">
+        <v>2.59</v>
+      </c>
+      <c r="AB6">
+        <v>1.39</v>
+      </c>
+      <c r="AC6">
+        <v>5.1</v>
+      </c>
+      <c r="AD6">
+        <v>1.1</v>
+      </c>
+      <c r="AE6">
+        <v>1.03</v>
+      </c>
+      <c r="AF6">
+        <v>2.1</v>
+      </c>
+      <c r="AG6">
+        <v>1.65</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.36</v>
       </c>
-      <c r="T6">
-        <v>2.9</v>
-      </c>
-      <c r="U6">
-        <v>2.7</v>
-      </c>
-      <c r="V6">
-        <v>1.38</v>
-      </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.28</v>
-      </c>
-      <c r="Z6">
-        <v>3.4</v>
-      </c>
-      <c r="AA6">
-        <v>1.9</v>
-      </c>
-      <c r="AB6">
-        <v>1.79</v>
-      </c>
-      <c r="AC6">
-        <v>3.2</v>
-      </c>
-      <c r="AD6">
+      <c r="AK6">
         <v>1.27</v>
-      </c>
-      <c r="AE6">
-        <v>1.07</v>
-      </c>
-      <c r="AF6">
-        <v>2.65</v>
-      </c>
-      <c r="AG6">
-        <v>1.37</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.12</v>
-      </c>
-      <c r="AK6">
-        <v>3.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="O7">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="P7">
-        <v>2.19</v>
+        <v>7.34</v>
       </c>
       <c r="Q7">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>2.59</v>
       </c>
       <c r="S7">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
         <v>1.04</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
+        <v>3.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.9</v>
+      </c>
+      <c r="AB7">
+        <v>1.83</v>
+      </c>
+      <c r="AC7">
+        <v>3.36</v>
+      </c>
+      <c r="AD7">
+        <v>1.3</v>
+      </c>
+      <c r="AE7">
         <v>1.11</v>
       </c>
-      <c r="Y7">
-        <v>1.55</v>
-      </c>
-      <c r="Z7">
-        <v>2.35</v>
-      </c>
-      <c r="AA7">
-        <v>2.7</v>
-      </c>
-      <c r="AB7">
-        <v>1.44</v>
-      </c>
-      <c r="AC7">
-        <v>5.25</v>
-      </c>
-      <c r="AD7">
-        <v>1.14</v>
-      </c>
-      <c r="AE7">
-        <v>1.01</v>
-      </c>
       <c r="AF7">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,49 +1613,49 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>4.4</v>
+        <v>5.53</v>
       </c>
       <c r="Q8">
         <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U8">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="V8">
         <v>1.3</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AA8">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC8">
         <v>4.33</v>
@@ -1664,13 +1664,13 @@
         <v>1.18</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AG8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.1</v>
       </c>
       <c r="AK8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
         <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="R13">
         <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T13">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="U13">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
         <v>1.05</v>
@@ -2461,28 +2461,28 @@
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Z13">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AA13">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD13">
         <v>1.11</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG13">
         <v>1.48</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "90"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1255,139 +1255,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.75</v>
+        <v>1.37</v>
       </c>
       <c r="O6">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>2.15</v>
+        <v>7.34</v>
       </c>
       <c r="Q6">
+        <v>1.8</v>
+      </c>
+      <c r="R6">
+        <v>2.59</v>
+      </c>
+      <c r="S6">
+        <v>1.36</v>
+      </c>
+      <c r="T6">
+        <v>3.2</v>
+      </c>
+      <c r="U6">
+        <v>2.65</v>
+      </c>
+      <c r="V6">
+        <v>1.42</v>
+      </c>
+      <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>1.29</v>
+      </c>
+      <c r="Z6">
+        <v>3.4</v>
+      </c>
+      <c r="AA6">
+        <v>1.9</v>
+      </c>
+      <c r="AB6">
+        <v>1.83</v>
+      </c>
+      <c r="AC6">
+        <v>3.36</v>
+      </c>
+      <c r="AD6">
+        <v>1.3</v>
+      </c>
+      <c r="AE6">
+        <v>1.11</v>
+      </c>
+      <c r="AF6">
+        <v>2.38</v>
+      </c>
+      <c r="AG6">
+        <v>1.37</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>["45+2", "48"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.12</v>
+      </c>
+      <c r="AK6">
+        <v>3.5</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>4</v>
       </c>
-      <c r="R6">
-        <v>1.92</v>
-      </c>
-      <c r="S6">
-        <v>1.63</v>
-      </c>
-      <c r="T6">
-        <v>2.13</v>
-      </c>
-      <c r="U6">
-        <v>3.9</v>
-      </c>
-      <c r="V6">
-        <v>1.2</v>
-      </c>
-      <c r="W6">
-        <v>1.02</v>
-      </c>
-      <c r="X6">
-        <v>1.11</v>
-      </c>
-      <c r="Y6">
-        <v>1.55</v>
-      </c>
-      <c r="Z6">
-        <v>2.35</v>
-      </c>
-      <c r="AA6">
-        <v>2.59</v>
-      </c>
-      <c r="AB6">
-        <v>1.39</v>
-      </c>
-      <c r="AC6">
-        <v>5.1</v>
-      </c>
-      <c r="AD6">
-        <v>1.1</v>
-      </c>
-      <c r="AE6">
-        <v>1.03</v>
-      </c>
-      <c r="AF6">
-        <v>2.1</v>
-      </c>
-      <c r="AG6">
-        <v>1.65</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.36</v>
-      </c>
-      <c r="AK6">
-        <v>1.27</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.37</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>7.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="R7">
+        <v>1.92</v>
+      </c>
+      <c r="S7">
+        <v>1.63</v>
+      </c>
+      <c r="T7">
+        <v>2.13</v>
+      </c>
+      <c r="U7">
+        <v>3.9</v>
+      </c>
+      <c r="V7">
+        <v>1.2</v>
+      </c>
+      <c r="W7">
+        <v>1.02</v>
+      </c>
+      <c r="X7">
+        <v>1.11</v>
+      </c>
+      <c r="Y7">
+        <v>1.55</v>
+      </c>
+      <c r="Z7">
+        <v>2.35</v>
+      </c>
+      <c r="AA7">
         <v>2.59</v>
       </c>
-      <c r="S7">
+      <c r="AB7">
+        <v>1.39</v>
+      </c>
+      <c r="AC7">
+        <v>5.1</v>
+      </c>
+      <c r="AD7">
+        <v>1.1</v>
+      </c>
+      <c r="AE7">
+        <v>1.03</v>
+      </c>
+      <c r="AF7">
+        <v>2.1</v>
+      </c>
+      <c r="AG7">
+        <v>1.65</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.36</v>
       </c>
-      <c r="T7">
-        <v>3.2</v>
-      </c>
-      <c r="U7">
-        <v>2.65</v>
-      </c>
-      <c r="V7">
-        <v>1.42</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.29</v>
-      </c>
-      <c r="Z7">
-        <v>3.4</v>
-      </c>
-      <c r="AA7">
-        <v>1.9</v>
-      </c>
-      <c r="AB7">
-        <v>1.83</v>
-      </c>
-      <c r="AC7">
-        <v>3.36</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
-      <c r="AE7">
-        <v>1.11</v>
-      </c>
-      <c r="AF7">
-        <v>2.38</v>
-      </c>
-      <c r="AG7">
-        <v>1.37</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.12</v>
-      </c>
       <c r="AK7">
-        <v>3.5</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="O9">
         <v>3.25</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T9">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
         <v>3.34</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z9">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="AA9">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
+        <v>1.34</v>
+      </c>
+      <c r="T10">
+        <v>3.27</v>
+      </c>
+      <c r="U10">
+        <v>2.62</v>
+      </c>
+      <c r="V10">
+        <v>1.47</v>
+      </c>
+      <c r="W10">
+        <v>1.1</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.19</v>
+      </c>
+      <c r="Z10">
+        <v>3.9</v>
+      </c>
+      <c r="AA10">
+        <v>1.78</v>
+      </c>
+      <c r="AB10">
+        <v>1.98</v>
+      </c>
+      <c r="AC10">
+        <v>2.93</v>
+      </c>
+      <c r="AD10">
         <v>1.36</v>
       </c>
-      <c r="T10">
-        <v>2.88</v>
-      </c>
-      <c r="U10">
-        <v>2.75</v>
-      </c>
-      <c r="V10">
-        <v>1.36</v>
-      </c>
-      <c r="W10">
-        <v>1.08</v>
-      </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1.3</v>
-      </c>
-      <c r="Z10">
-        <v>3</v>
-      </c>
-      <c r="AA10">
-        <v>1.87</v>
-      </c>
-      <c r="AB10">
-        <v>1.83</v>
-      </c>
-      <c r="AC10">
-        <v>3.35</v>
-      </c>
-      <c r="AD10">
-        <v>1.27</v>
-      </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P11">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -2117,49 +2117,49 @@
         <v>2.7</v>
       </c>
       <c r="S11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U11">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="V11">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z11">
         <v>6.5</v>
       </c>
       <c r="AA11">
+        <v>1.3</v>
+      </c>
+      <c r="AB11">
+        <v>2.74</v>
+      </c>
+      <c r="AC11">
+        <v>1.95</v>
+      </c>
+      <c r="AD11">
+        <v>1.77</v>
+      </c>
+      <c r="AE11">
         <v>1.36</v>
       </c>
-      <c r="AB11">
-        <v>2.88</v>
-      </c>
-      <c r="AC11">
-        <v>2.1</v>
-      </c>
-      <c r="AD11">
+      <c r="AF11">
         <v>1.73</v>
       </c>
-      <c r="AE11">
-        <v>1.27</v>
-      </c>
-      <c r="AF11">
-        <v>1.72</v>
-      </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK11">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="P12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R12">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="S12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U12">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W12">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,28 +2301,28 @@
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA12">
         <v>1.36</v>
       </c>
       <c r="AB12">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AC12">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AD12">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE12">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF12">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG12">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
         <v>3.65</v>
@@ -2600,55 +2600,55 @@
         <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
         <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AA14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="AD14">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
+        <v>1.2</v>
+      </c>
+      <c r="O15">
+        <v>6.75</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>1.5</v>
+      </c>
+      <c r="R15">
+        <v>3.6</v>
+      </c>
+      <c r="S15">
+        <v>1.18</v>
+      </c>
+      <c r="T15">
+        <v>4.5</v>
+      </c>
+      <c r="U15">
+        <v>1.83</v>
+      </c>
+      <c r="V15">
+        <v>1.83</v>
+      </c>
+      <c r="W15">
+        <v>1.2</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.03</v>
+      </c>
+      <c r="Z15">
+        <v>7.2</v>
+      </c>
+      <c r="AA15">
+        <v>1.36</v>
+      </c>
+      <c r="AB15">
+        <v>3.1</v>
+      </c>
+      <c r="AC15">
+        <v>1.66</v>
+      </c>
+      <c r="AD15">
+        <v>2</v>
+      </c>
+      <c r="AE15">
+        <v>1.44</v>
+      </c>
+      <c r="AF15">
+        <v>1.76</v>
+      </c>
+      <c r="AG15">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.05</v>
       </c>
-      <c r="O15">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="P15">
-        <v>15</v>
-      </c>
-      <c r="Q15">
-        <v>1.3</v>
-      </c>
-      <c r="R15">
-        <v>3.15</v>
-      </c>
-      <c r="S15">
-        <v>1.11</v>
-      </c>
-      <c r="T15">
-        <v>6</v>
-      </c>
-      <c r="U15">
-        <v>1.74</v>
-      </c>
-      <c r="V15">
-        <v>1.97</v>
-      </c>
-      <c r="W15">
-        <v>1.4</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1.01</v>
-      </c>
-      <c r="Z15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA15">
-        <v>1.18</v>
-      </c>
-      <c r="AB15">
-        <v>3.92</v>
-      </c>
-      <c r="AC15">
-        <v>1.38</v>
-      </c>
-      <c r="AD15">
-        <v>2.63</v>
-      </c>
-      <c r="AE15">
-        <v>1.6</v>
-      </c>
-      <c r="AF15">
-        <v>1.91</v>
-      </c>
-      <c r="AG15">
-        <v>1.68</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.01</v>
-      </c>
       <c r="AK15">
-        <v>8</v>
+        <v>3.48</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-08-27.xlsx
+++ b/jogos_2026-08-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU15"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "77"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "51", "82"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1605,119 +1605,119 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>5.53</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
+        <v>2.75</v>
+      </c>
+      <c r="R8">
+        <v>2.05</v>
+      </c>
+      <c r="S8">
+        <v>1.49</v>
+      </c>
+      <c r="T8">
+        <v>2.63</v>
+      </c>
+      <c r="U8">
+        <v>3.34</v>
+      </c>
+      <c r="V8">
+        <v>1.29</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.39</v>
+      </c>
+      <c r="Z8">
+        <v>2.72</v>
+      </c>
+      <c r="AA8">
         <v>2.38</v>
       </c>
-      <c r="R8">
-        <v>2.12</v>
-      </c>
-      <c r="S8">
-        <v>1.51</v>
-      </c>
-      <c r="T8">
-        <v>2.31</v>
-      </c>
-      <c r="U8">
-        <v>3.25</v>
-      </c>
-      <c r="V8">
-        <v>1.3</v>
-      </c>
-      <c r="W8">
-        <v>1.04</v>
-      </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
-      <c r="Y8">
-        <v>1.36</v>
-      </c>
-      <c r="Z8">
-        <v>2.6</v>
-      </c>
-      <c r="AA8">
-        <v>2.35</v>
-      </c>
       <c r="AB8">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC8">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "64"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-27 15:00:00</t>
+          <t>2026-08-27 15:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,25 +1744,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1772,115 +1772,115 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="Q9">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>3.27</v>
       </c>
       <c r="U9">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>4.15</v>
+        <v>2.93</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
+        <v>1.6</v>
+      </c>
+      <c r="AG9">
+        <v>2.15</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["3"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.25</v>
+      </c>
+      <c r="AK9">
+        <v>1.5</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>2</v>
       </c>
-      <c r="AG9">
-        <v>1.8</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.2</v>
-      </c>
-      <c r="AK9">
-        <v>1.85</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1</v>
-      </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-27 15:30:00</t>
+          <t>2026-08-27 15:45:00</t>
         </is>
       </c>
     </row>
@@ -1892,158 +1892,158 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="P10">
-        <v>2.98</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="T10">
-        <v>3.27</v>
+        <v>4.5</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="W10">
+        <v>1.22</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
         <v>1.1</v>
       </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.19</v>
-      </c>
       <c r="Z10">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA10">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
       <c r="AC10">
-        <v>2.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD10">
+        <v>1.77</v>
+      </c>
+      <c r="AE10">
         <v>1.36</v>
       </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "11"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "69"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-27 15:45:00</t>
+          <t>2026-08-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,76 +2060,76 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
         <v>1.22</v>
       </c>
       <c r="O11">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="S11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T11">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U11">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="W11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2141,68 +2141,68 @@
         <v>6.5</v>
       </c>
       <c r="AA11">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB11">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="AC11">
+        <v>1.89</v>
+      </c>
+      <c r="AD11">
+        <v>1.8</v>
+      </c>
+      <c r="AE11">
+        <v>1.35</v>
+      </c>
+      <c r="AF11">
+        <v>1.74</v>
+      </c>
+      <c r="AG11">
         <v>1.95</v>
       </c>
-      <c r="AD11">
-        <v>1.77</v>
-      </c>
-      <c r="AE11">
-        <v>1.36</v>
-      </c>
-      <c r="AF11">
-        <v>1.73</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["37", "82"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>6.7</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="Q12">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="V12">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="W12">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA12">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>1.89</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>3.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:00:00</t>
+          <t>2026-08-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="P13">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>3.55</v>
       </c>
       <c r="S13">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>3.32</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.91</v>
       </c>
       <c r="W13">
+        <v>1.22</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.03</v>
+      </c>
+      <c r="Z13">
+        <v>7.6</v>
+      </c>
+      <c r="AA13">
+        <v>1.33</v>
+      </c>
+      <c r="AB13">
+        <v>3.4</v>
+      </c>
+      <c r="AC13">
+        <v>1.66</v>
+      </c>
+      <c r="AD13">
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>1.44</v>
+      </c>
+      <c r="AF13">
+        <v>1.69</v>
+      </c>
+      <c r="AG13">
+        <v>1.95</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.05</v>
       </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>1.41</v>
-      </c>
-      <c r="Z13">
-        <v>2.52</v>
-      </c>
-      <c r="AA13">
-        <v>2.35</v>
-      </c>
-      <c r="AB13">
-        <v>1.55</v>
-      </c>
-      <c r="AC13">
-        <v>4.33</v>
-      </c>
-      <c r="AD13">
-        <v>1.11</v>
-      </c>
-      <c r="AE13">
-        <v>1.05</v>
-      </c>
-      <c r="AF13">
-        <v>2.45</v>
-      </c>
-      <c r="AG13">
-        <v>1.48</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.19</v>
-      </c>
       <c r="AK13">
-        <v>2.08</v>
+        <v>3.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2531,332 +2531,6 @@
         <v>0</v>
       </c>
       <c r="AU13" t="inlineStr">
-        <is>
-          <t>2026-08-27 17:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N14">
-        <v>1.8</v>
-      </c>
-      <c r="O14">
-        <v>3.65</v>
-      </c>
-      <c r="P14">
-        <v>3.45</v>
-      </c>
-      <c r="Q14">
-        <v>2.4</v>
-      </c>
-      <c r="R14">
-        <v>2.3</v>
-      </c>
-      <c r="S14">
-        <v>1.25</v>
-      </c>
-      <c r="T14">
-        <v>3.12</v>
-      </c>
-      <c r="U14">
-        <v>2.23</v>
-      </c>
-      <c r="V14">
-        <v>1.5</v>
-      </c>
-      <c r="W14">
-        <v>1.14</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.15</v>
-      </c>
-      <c r="Z14">
-        <v>4.3</v>
-      </c>
-      <c r="AA14">
-        <v>1.5</v>
-      </c>
-      <c r="AB14">
-        <v>2.15</v>
-      </c>
-      <c r="AC14">
-        <v>2.55</v>
-      </c>
-      <c r="AD14">
-        <v>1.44</v>
-      </c>
-      <c r="AE14">
-        <v>1.14</v>
-      </c>
-      <c r="AF14">
-        <v>1.53</v>
-      </c>
-      <c r="AG14">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.29</v>
-      </c>
-      <c r="AK14">
-        <v>1.8</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2026-08-27 19:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N15">
-        <v>1.2</v>
-      </c>
-      <c r="O15">
-        <v>6.75</v>
-      </c>
-      <c r="P15">
-        <v>10</v>
-      </c>
-      <c r="Q15">
-        <v>1.5</v>
-      </c>
-      <c r="R15">
-        <v>3.6</v>
-      </c>
-      <c r="S15">
-        <v>1.18</v>
-      </c>
-      <c r="T15">
-        <v>4.5</v>
-      </c>
-      <c r="U15">
-        <v>1.83</v>
-      </c>
-      <c r="V15">
-        <v>1.83</v>
-      </c>
-      <c r="W15">
-        <v>1.2</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.03</v>
-      </c>
-      <c r="Z15">
-        <v>7.2</v>
-      </c>
-      <c r="AA15">
-        <v>1.36</v>
-      </c>
-      <c r="AB15">
-        <v>3.1</v>
-      </c>
-      <c r="AC15">
-        <v>1.66</v>
-      </c>
-      <c r="AD15">
-        <v>2</v>
-      </c>
-      <c r="AE15">
-        <v>1.44</v>
-      </c>
-      <c r="AF15">
-        <v>1.76</v>
-      </c>
-      <c r="AG15">
-        <v>1.85</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.05</v>
-      </c>
-      <c r="AK15">
-        <v>3.48</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
         <is>
           <t>2026-08-27 21:30:00</t>
         </is>
